--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260624.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260624.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,51 +616,51 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.55%</t>
+          <t>26.74%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>ORCL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>115,830</t>
+          <t>18,275</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.37%</t>
+          <t>8.47%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>ORCL US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>18,275</t>
+          <t>115,830</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.28%</t>
+          <t>8.00%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.22%</t>
+          <t>7.16%</t>
         </is>
       </c>
     </row>
@@ -704,46 +704,46 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.32%</t>
+          <t>5.40%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>EQIX US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Equinix公司</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>6,565</t>
+          <t>75,875</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.18%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>EQIX US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>Equinix公司</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>75,875</t>
+          <t>6,565</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -755,44 +755,44 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>68,880</t>
+          <t>52,335</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>2.89%</t>
+          <t>2.90%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>52,335</t>
+          <t>68,880</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.83%</t>
         </is>
       </c>
     </row>
@@ -814,469 +814,469 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.69%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>166,669,167</t>
+          <t>36,530</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.16%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>36,530</t>
+          <t>21,183</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>21,183</t>
+          <t>23,545</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>HPE US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>慧與</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>23,545</t>
+          <t>89,195</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>HPE US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>慧與</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>89,195</t>
+          <t>59,155</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.80%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>59,155</t>
+          <t>9,300</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.77%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>13,611</t>
+          <t>22,600</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>9,300</t>
+          <t>30,798</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>22,600</t>
+          <t>13,611</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>30,798</t>
+          <t>41,980</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>愛克斯龍公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>41,980</t>
+          <t>68,868</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>愛克斯龍公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>68,868</t>
+          <t>11,196</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>11,196</t>
+          <t>89,993,363</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>C_USD</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>2,942,745</t>
+          <t>24,738</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.20%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>24,738</t>
+          <t>147,015</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>147,015</t>
+          <t>21,455</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>21,455</t>
+          <t>22,867</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>22,867</t>
+          <t>18,521</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>C_USD</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>18,521</t>
+          <t>1,942,745</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>NRG US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>NRG Energy Inc</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>43,480</t>
+          <t>13,665</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>NRG US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>NRG Energy Inc</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>13,665</t>
+          <t>43,480</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1298,29 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>RDI_NTD</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>31,605,000</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
